--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486424_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486424_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9354</v>
+        <v>1.5596</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1693</v>
+        <v>2.3928</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.234</v>
+        <v>-0.8333</v>
       </c>
       <c r="G2" t="n">
         <v>2.6819</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5067</v>
+        <v>0.1175</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6934</v>
+        <v>-0.4698</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1866</v>
+        <v>0.5873</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3698</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2027</v>
+        <v>-0.3091</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1439</v>
+        <v>0.2975</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0587</v>
+        <v>-0.6067</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.4331</v>
+        <v>-0.8962</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8545</v>
+        <v>-1.1862</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5786</v>
+        <v>0.29</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.1803</v>
+        <v>0.1677</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3222</v>
+        <v>0.0912</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8582</v>
+        <v>0.0765</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2528</v>
+        <v>-1.0639</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5324</v>
+        <v>-1.2775</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7204</v>
+        <v>0.2136</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3926</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3926</v>
+        <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9679</v>
+        <v>0.3695</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.3473</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1267</v>
+        <v>0.0222</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.706</v>
+        <v>-0.6814</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0377</v>
+        <v>-0.746</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6683</v>
+        <v>0.0645</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8962</v>
+        <v>-2.4331</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1862</v>
+        <v>-0.8545</v>
       </c>
       <c r="I4" t="n">
-        <v>0.29</v>
+        <v>-1.5786</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1677</v>
+        <v>-1.1803</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0912</v>
+        <v>-0.3222</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0765</v>
+        <v>-0.8582</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0639</v>
+        <v>-1.2528</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2775</v>
+        <v>-0.5324</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2136</v>
+        <v>-0.7204</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>2.3926</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0274</v>
+        <v>0.4891</v>
       </c>
       <c r="T4" t="n">
-        <v>0.012</v>
+        <v>0.2392</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0394</v>
+        <v>0.2499</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8589</v>
+        <v>-0.9745</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0505</v>
+        <v>-0.827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1916</v>
+        <v>-0.1475</v>
       </c>
       <c r="G5" t="n">
         <v>-2.4143</v>
@@ -844,13 +844,13 @@
         <v>2.8276</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5755</v>
+        <v>0.46</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6813</v>
+        <v>-0.4578</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2568</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7602</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0574</v>
+        <v>-1.2317</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0582</v>
+        <v>-2.3249</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0008</v>
+        <v>1.0933</v>
       </c>
       <c r="G6" t="n">
         <v>-2.7822</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0153</v>
+        <v>-0.1896</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3701</v>
+        <v>0.1034</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3854</v>
+        <v>-0.2929</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5401</v>
+        <v>-1.4476</v>
       </c>
       <c r="E7" t="n">
         <v>-1.8694</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3292</v>
+        <v>0.4217</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6993</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4058</v>
+        <v>-0.3133</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1694</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7706</v>
+        <v>-1.8447</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7184</v>
+        <v>0.6752</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.489</v>
+        <v>-2.5199</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3994</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7365</v>
+        <v>0.6624</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4951</v>
+        <v>0.4518</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2414</v>
+        <v>0.2106</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3252</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2818</v>
+        <v>-1.982</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8846</v>
+        <v>-2.3691</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6028</v>
+        <v>0.3871</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7573</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3049</v>
+        <v>-0.0051</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3184</v>
+        <v>0.1971</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0136</v>
+        <v>-0.2022</v>
       </c>
       <c r="V9" t="n">
         <v>1.5204</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9398</v>
+        <v>-3.7563</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1095</v>
+        <v>-1.8064</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1697</v>
+        <v>-1.9499</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9193</v>
+        <v>-1.6082</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3783</v>
+        <v>-0.3802</v>
       </c>
       <c r="I10" t="n">
-        <v>0.459</v>
+        <v>-1.228</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6451</v>
+        <v>-0.4064</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.1439</v>
+        <v>0.1857</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4989</v>
+        <v>-0.5921</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2742</v>
+        <v>-1.2018</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2344</v>
+        <v>-0.5659</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0399</v>
+        <v>-0.6359</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.305</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4145</v>
+        <v>-0.1481</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2019</v>
+        <v>-0.0949</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6163</v>
+        <v>-0.0532</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1339</v>
+        <v>-4.3222</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0299</v>
+        <v>-5.1528</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.104</v>
+        <v>0.8306</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6082</v>
+        <v>-1.9193</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3802</v>
+        <v>-2.3783</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.228</v>
+        <v>0.459</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4064</v>
+        <v>-1.6451</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1857</v>
+        <v>-2.1439</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5921</v>
+        <v>0.4989</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2018</v>
+        <v>-0.2742</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5659</v>
+        <v>-0.2344</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6359</v>
+        <v>-0.0399</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="R11" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5256999999999999</v>
+        <v>0.0321</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3184</v>
+        <v>-0.2451</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2073</v>
+        <v>0.2773</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4765</v>
+        <v>-4.7001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1481</v>
+        <v>-2.3716</v>
       </c>
       <c r="F12" t="n">
         <v>-2.3284</v>
@@ -1390,10 +1390,10 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5396</v>
+        <v>0.316</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0156</v>
+        <v>-0.2079</v>
       </c>
       <c r="U12" t="n">
         <v>0.5239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.0323</v>
+        <v>-19.69</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.4441</v>
+        <v>-14.1017</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.5883</v>
+        <v>-5.5885</v>
       </c>
       <c r="G13" t="n">
         <v>-16.3958</v>
@@ -1459,7 +1459,7 @@
         <v>-9.8614</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000199999999999978</v>
+        <v>0.0001999999999997559</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.4004</v>
@@ -1468,10 +1468,10 @@
         <v>17.4006</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4482</v>
+        <v>1.7905</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6488000000000002</v>
+        <v>-0.3060999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>2.0968</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8721</v>
+        <v>7.6885</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4873</v>
+        <v>4.3756</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3847</v>
+        <v>3.3129</v>
       </c>
       <c r="G14" t="n">
         <v>5.3468</v>
@@ -1546,13 +1546,13 @@
         <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.7342</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1454</v>
+        <v>-0.2572</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0632</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.2599</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8517</v>
+        <v>5.9827</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3345</v>
+        <v>2.3413</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5172</v>
+        <v>3.6414</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8024</v>
+        <v>4.8386</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2587</v>
+        <v>0.9731</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5437</v>
+        <v>3.8656</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7666</v>
+        <v>4.3878</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1365</v>
+        <v>0.3134</v>
       </c>
       <c r="L15" t="n">
-        <v>3.903</v>
+        <v>4.0744</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0358</v>
+        <v>0.4509</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3951</v>
+        <v>0.6597</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6407</v>
+        <v>-0.2088</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3204</v>
+        <v>-0.161</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.822</v>
+        <v>-0.9589</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5016</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.842</v>
+        <v>5.1138</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3413</v>
+        <v>1.3345</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5007</v>
+        <v>3.7793</v>
       </c>
       <c r="G16" t="n">
-        <v>4.8386</v>
+        <v>4.8024</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9731</v>
+        <v>0.2587</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8656</v>
+        <v>4.5437</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3878</v>
+        <v>3.7666</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3134</v>
+        <v>-0.1365</v>
       </c>
       <c r="L16" t="n">
-        <v>4.0744</v>
+        <v>3.903</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4509</v>
+        <v>1.0358</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6597</v>
+        <v>0.3951</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2088</v>
+        <v>0.6407</v>
       </c>
       <c r="P16" t="n">
-        <v>1.305</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3017</v>
+        <v>-0.0583</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9589</v>
+        <v>-0.822</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3427</v>
+        <v>0.7637</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2283</v>
+        <v>3.5636</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1366</v>
+        <v>3.0249</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0917</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>3.0469</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0361</v>
+        <v>0.2992</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4026</v>
+        <v>0.2908</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4386</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9224</v>
+        <v>3.1164</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6441</v>
+        <v>0.7558</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2783</v>
+        <v>2.3606</v>
       </c>
       <c r="G18" t="n">
         <v>0.8708</v>
@@ -1858,13 +1858,13 @@
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0941</v>
+        <v>0.2881</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U18" t="n">
-        <v>0.779</v>
+        <v>0.8613</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6875</v>
+        <v>2.227</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6589</v>
+        <v>2.1059</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0286</v>
+        <v>0.121</v>
       </c>
       <c r="G19" t="n">
         <v>1.1241</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1114</v>
+        <v>0.4281</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.137</v>
+        <v>0.31</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0256</v>
+        <v>0.1181</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1006</v>
+        <v>0.292</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.858</v>
+        <v>-1.4167</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9586</v>
+        <v>1.7087</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0363</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3767</v>
+        <v>0.5681</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0106</v>
+        <v>0.4518</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6339</v>
+        <v>0.1163</v>
       </c>
       <c r="V20" t="n">
         <v>0.1952</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7988</v>
+        <v>-0.1001</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3355</v>
+        <v>-3.6065</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5368000000000001</v>
+        <v>3.5064</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8548</v>
+        <v>-1.0032</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4142</v>
+        <v>1.8519</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5594</v>
+        <v>-2.8551</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0286</v>
+        <v>-1.439</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.1642</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0765</v>
+        <v>-1.6032</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1738</v>
+        <v>0.4358</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4621</v>
+        <v>1.6877</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6359</v>
+        <v>-1.2519</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.6976</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.216</v>
+        <v>0.1854</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.274</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.058</v>
+        <v>0.8956</v>
       </c>
       <c r="V21" t="n">
-        <v>2.2599</v>
+        <v>-0.3698</v>
       </c>
       <c r="W21" t="n">
-        <v>2.2599</v>
+        <v>-0.3698</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8746</v>
+        <v>-0.4185</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7182</v>
+        <v>-1.3355</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8436</v>
+        <v>0.917</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0032</v>
+        <v>0.8548</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8519</v>
+        <v>1.4142</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8551</v>
+        <v>-0.5594</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.439</v>
+        <v>1.0286</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1642</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6032</v>
+        <v>0.0765</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4358</v>
+        <v>-0.1738</v>
       </c>
       <c r="N22" t="n">
-        <v>1.6877</v>
+        <v>0.4621</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2519</v>
+        <v>-0.6359</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0875</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5891999999999999</v>
+        <v>0.1643</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.822</v>
+        <v>-0.274</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2328</v>
+        <v>0.4383</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3698</v>
+        <v>2.2599</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3698</v>
+        <v>2.2599</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.673</v>
+        <v>-1.19</v>
       </c>
       <c r="E23" t="n">
         <v>-0.2945</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3785</v>
+        <v>-0.8955</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0632</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0428</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>0.4026</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3598</v>
+        <v>0.1232</v>
       </c>
       <c r="V23" t="n">
         <v>0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1259</v>
+        <v>-1.7726</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8081</v>
+        <v>-1.6963</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3178</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-1.386</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3049</v>
+        <v>0.0484</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2364</v>
+        <v>0.0051</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>20.0323</v>
+        <v>24.5028</v>
       </c>
       <c r="E25" t="n">
-        <v>5.588400000000002</v>
+        <v>5.5885</v>
       </c>
       <c r="F25" t="n">
-        <v>14.4439</v>
+        <v>18.9143</v>
       </c>
       <c r="G25" t="n">
         <v>16.3957</v>
@@ -2383,19 +2383,19 @@
         <v>8.2285</v>
       </c>
       <c r="L25" t="n">
-        <v>9.861400000000001</v>
+        <v>9.8614</v>
       </c>
       <c r="M25" t="n">
         <v>-1.6944</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1188</v>
+        <v>4.118799999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-5.8134</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.775557561562891e-16</v>
+        <v>-6.106226635438361e-16</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.4004</v>
@@ -2404,13 +2404,13 @@
         <v>17.4006</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4483</v>
+        <v>3.0222</v>
       </c>
       <c r="T25" t="n">
         <v>-2.097</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6488</v>
+        <v>5.119299999999999</v>
       </c>
       <c r="V25" t="n">
         <v>5.0848</v>
